--- a/data/trans_orig/IP1014-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1014-Estudios-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3098</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4515</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87362</t>
+          <t>87638</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83620</t>
+          <t>83747</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>173197</t>
+          <t>173186</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>5751</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>678</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>470786</t>
+          <t>471240</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>476311</t>
+          <t>476312</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>887550</t>
+          <t>887539</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>892402</t>
+          <t>892400</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154319</t>
+          <t>154758</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>328539</t>
+          <t>328837</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>7544</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8694</t>
+          <t>8862</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>678079</t>
+          <t>677995</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>714513</t>
+          <t>714430</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>720626</t>
+          <t>720658</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1394301</t>
+          <t>1394133</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1401635</t>
+          <t>1401622</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3421</t>
+          <t>3641</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80019</t>
+          <t>80418</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>172004</t>
+          <t>171784</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7916</t>
+          <t>7342</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1473</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8531</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>444466</t>
+          <t>443998</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>484488</t>
+          <t>485062</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>491137</t>
+          <t>491172</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>933572</t>
+          <t>932702</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>940725</t>
+          <t>940630</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>2537</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4069</t>
+          <t>4154</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>163127</t>
+          <t>162803</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>167398</t>
+          <t>167624</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>332832</t>
+          <t>332747</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>6325</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9306</t>
+          <t>9095</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11253</t>
+          <t>11057</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>702001</t>
+          <t>700603</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>738195</t>
+          <t>738406</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>745561</t>
+          <t>745533</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1443176</t>
+          <t>1443372</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1451341</t>
+          <t>1451531</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65213</t>
+          <t>65157</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>124686</t>
+          <t>124018</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4351</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>484035</t>
+          <t>484384</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>956775</t>
+          <t>956414</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5002,47 +5002,47 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>617</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5357</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
-      </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>739487</t>
+          <t>739598</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>744227</t>
+          <t>744225</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1443872</t>
+          <t>1443342</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1448600</t>
+          <t>1448598</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">

--- a/data/trans_orig/IP1014-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1014-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -737,92 +737,92 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,93%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3901</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3098</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4472</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4526</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>86203</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>83428</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,26%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,07%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>90225</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>87638</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>86966</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,29%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,45%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,71%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>86203</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>83747</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>96,43%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>264</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>173186</t>
+          <t>173240</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,92 +1065,92 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5584</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>2084</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5751</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2084</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>677</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>474907</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>471407</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>476313</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,83%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,86%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>474907</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>471240</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>476312</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,79%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,86%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1344</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>887539</t>
+          <t>887519</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>892400</t>
+          <t>892401</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3383</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>673</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3380</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3677</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3368</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>157465</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>154755</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,86%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>157465</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>154758</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,86%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>489</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>328837</t>
+          <t>328528</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3399</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1313</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7368</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3026</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3590</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3399</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1316</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7544</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>8679</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>718575</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>714606</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>720661</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,53%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,98%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1017</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>680379</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>677995</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>677431</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,91%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>99,47%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>718575</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>714430</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>720658</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2097</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1394133</t>
+          <t>1394316</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1401622</t>
+          <t>1401240</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2325,107 +2325,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>624</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3119</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4242</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3641</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -2438,74 +2438,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>82913</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>80427</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,28%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>82913</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>96,27%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>249</t>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>171784</t>
+          <t>171183</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2668,72 +2668,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3275</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7294</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5702</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4495</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3275</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1232</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7342</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9401</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -2781,74 +2781,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>489129</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>485110</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>491168</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,33%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,75%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>650</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>448804</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>443998</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>445205</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,8%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,73%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>99,0%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>489129</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>485062</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>491172</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,33%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,51%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,75%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1350</t>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>932702</t>
+          <t>933123</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>940630</t>
+          <t>940725</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>651</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3016,102 +3016,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3752</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>443</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2537</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2143</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,27%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>793</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3937</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4182</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1236</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4154</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -3124,74 +3124,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>170768</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>167809</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,54%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,81%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>164897</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>162803</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>163197</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,73%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>98,47%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,7%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>170768</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>167624</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,54%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,71%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>475</t>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>332747</t>
+          <t>332719</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3354,72 +3354,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4691</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9527</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1339</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6325</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5560</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4691</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9095</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11057</t>
+          <t>11240</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -3467,74 +3467,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>742810</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>737974</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>745506</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,73%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>705589</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>700603</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>701368</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>742810</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>738406</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>745533</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,78%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2074</t>
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1443372</t>
+          <t>1443189</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1451531</t>
+          <t>1451558</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3928,107 +3928,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4131</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>662</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3457</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3697</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>662</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3975</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -4041,74 +4041,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>67952</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>64483</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,03%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,98%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>67952</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>65157</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,03%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>94,96%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>187</t>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>124018</t>
+          <t>124296</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4271,92 +4271,92 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1333</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4107</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1333</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4351</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1333</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>4661</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4384,74 +4384,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>693</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>487402</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>484628</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>99,16%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>693</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>487402</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>484384</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1407</t>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>956414</t>
+          <t>956364</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4727,47 +4727,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4957,84 +4957,84 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5701</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1995</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5246</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
           <t>617</t>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -5070,74 +5070,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>742849</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>739143</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>744250</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>742849</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>739598</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>744225</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2123</t>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1443342</t>
+          <t>1443163</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
